--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/127.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/127.xlsx
@@ -426,13 +426,13 @@
         <v>-16.73671526147678</v>
       </c>
       <c r="E2">
-        <v>-10.19430803839278</v>
+        <v>-8.904598641008263</v>
       </c>
       <c r="F2">
-        <v>-5.012332845048716</v>
+        <v>-5.461615301672486</v>
       </c>
       <c r="G2">
-        <v>-6.884869876688757</v>
+        <v>-5.667380338620847</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.46348775230724</v>
       </c>
       <c r="E3">
-        <v>-9.771629331464846</v>
+        <v>-9.302429611056112</v>
       </c>
       <c r="F3">
-        <v>-4.560129564962674</v>
+        <v>-5.494979455555042</v>
       </c>
       <c r="G3">
-        <v>-6.569997269357597</v>
+        <v>-5.505878685033041</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.10512499369256</v>
       </c>
       <c r="E4">
-        <v>-10.50818562881243</v>
+        <v>-10.90973447602057</v>
       </c>
       <c r="F4">
-        <v>-4.650351200638583</v>
+        <v>-5.541360574805189</v>
       </c>
       <c r="G4">
-        <v>-6.129969487914289</v>
+        <v>-5.527864017959341</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.68503089961001</v>
       </c>
       <c r="E5">
-        <v>-12.06329077389048</v>
+        <v>-10.73707734753013</v>
       </c>
       <c r="F5">
-        <v>-4.628642176113416</v>
+        <v>-5.484091394412646</v>
       </c>
       <c r="G5">
-        <v>-6.416060212327025</v>
+        <v>-5.326149167706008</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.20945416332516</v>
       </c>
       <c r="E6">
-        <v>-12.13493123269182</v>
+        <v>-11.88632253814473</v>
       </c>
       <c r="F6">
-        <v>-5.116652465552868</v>
+        <v>-5.167877877374587</v>
       </c>
       <c r="G6">
-        <v>-5.957380817315463</v>
+        <v>-4.809727237398478</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.69276426065254</v>
       </c>
       <c r="E7">
-        <v>-12.37219157137569</v>
+        <v>-12.90092261108926</v>
       </c>
       <c r="F7">
-        <v>-4.966820683204105</v>
+        <v>-5.343348459207398</v>
       </c>
       <c r="G7">
-        <v>-6.359655137428923</v>
+        <v>-5.452459722211361</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.12958656747481</v>
       </c>
       <c r="E8">
-        <v>-12.05335077344364</v>
+        <v>-12.88001011812184</v>
       </c>
       <c r="F8">
-        <v>-4.477938122889505</v>
+        <v>-5.466180434429314</v>
       </c>
       <c r="G8">
-        <v>-5.872117716951534</v>
+        <v>-5.237251088339959</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.5255400160752</v>
       </c>
       <c r="E9">
-        <v>-13.47085823579862</v>
+        <v>-13.97855904222057</v>
       </c>
       <c r="F9">
-        <v>-4.740027770563448</v>
+        <v>-5.045225657879079</v>
       </c>
       <c r="G9">
-        <v>-5.634913818517214</v>
+        <v>-5.050480040650896</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.88232789621542</v>
       </c>
       <c r="E10">
-        <v>-15.14585473022974</v>
+        <v>-15.53371852898671</v>
       </c>
       <c r="F10">
-        <v>-4.406918043610489</v>
+        <v>-5.326187171723601</v>
       </c>
       <c r="G10">
-        <v>-5.18932432056793</v>
+        <v>-4.375396904828255</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.20849574900972</v>
       </c>
       <c r="E11">
-        <v>-16.46468674395759</v>
+        <v>-15.95347184170569</v>
       </c>
       <c r="F11">
-        <v>-4.614769507218733</v>
+        <v>-4.81326870284937</v>
       </c>
       <c r="G11">
-        <v>-4.931793672522486</v>
+        <v>-4.059739698204287</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.52908241367496</v>
       </c>
       <c r="E12">
-        <v>-16.95075503004489</v>
+        <v>-15.7519185205723</v>
       </c>
       <c r="F12">
-        <v>-4.718504300336509</v>
+        <v>-4.852520063863621</v>
       </c>
       <c r="G12">
-        <v>-4.69743022216086</v>
+        <v>-4.317247172430957</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.86674104542405</v>
       </c>
       <c r="E13">
-        <v>-16.47979826172118</v>
+        <v>-17.1591644608259</v>
       </c>
       <c r="F13">
-        <v>-4.509249582347923</v>
+        <v>-4.85754991073342</v>
       </c>
       <c r="G13">
-        <v>-4.480655700249383</v>
+        <v>-3.726328035853207</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.26159470126165</v>
       </c>
       <c r="E14">
-        <v>-18.33925761638075</v>
+        <v>-17.73596525213089</v>
       </c>
       <c r="F14">
-        <v>-4.517290544726897</v>
+        <v>-4.544367390022205</v>
       </c>
       <c r="G14">
-        <v>-5.261255854045214</v>
+        <v>-3.774516336722839</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.751545285437595</v>
       </c>
       <c r="E15">
-        <v>-19.44645139736012</v>
+        <v>-18.41626431688118</v>
       </c>
       <c r="F15">
-        <v>-4.097546841319555</v>
+        <v>-4.542197895794273</v>
       </c>
       <c r="G15">
-        <v>-3.944989568722069</v>
+        <v>-3.077305514515709</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.358056776906084</v>
       </c>
       <c r="E16">
-        <v>-19.05307644573582</v>
+        <v>-20.07844070139659</v>
       </c>
       <c r="F16">
-        <v>-3.659217886863002</v>
+        <v>-4.161883652392784</v>
       </c>
       <c r="G16">
-        <v>-3.683486266029499</v>
+        <v>-2.820092678842034</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.096367210174389</v>
       </c>
       <c r="E17">
-        <v>-20.81110251109757</v>
+        <v>-20.73074473983146</v>
       </c>
       <c r="F17">
-        <v>-3.707617737473771</v>
+        <v>-4.254883632337681</v>
       </c>
       <c r="G17">
-        <v>-3.149054967988333</v>
+        <v>-3.005751383229901</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.965992073332707</v>
       </c>
       <c r="E18">
-        <v>-21.28423294694496</v>
+        <v>-21.14985500924135</v>
       </c>
       <c r="F18">
-        <v>-3.649963366238926</v>
+        <v>-3.618975798435002</v>
       </c>
       <c r="G18">
-        <v>-3.947422819693434</v>
+        <v>-2.994465733486526</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.954095009395754</v>
       </c>
       <c r="E19">
-        <v>-21.66340660408121</v>
+        <v>-21.3969557219439</v>
       </c>
       <c r="F19">
-        <v>-3.302940380388546</v>
+        <v>-3.489679244001638</v>
       </c>
       <c r="G19">
-        <v>-5.080708631969982</v>
+        <v>-3.418510201066233</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.0505312283224</v>
       </c>
       <c r="E20">
-        <v>-21.41499716239045</v>
+        <v>-23.12512555817308</v>
       </c>
       <c r="F20">
-        <v>-2.770691958169988</v>
+        <v>-3.009588146932948</v>
       </c>
       <c r="G20">
-        <v>-3.756189156617433</v>
+        <v>-4.199477825416924</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.23268686695649</v>
       </c>
       <c r="E21">
-        <v>-22.36369888157537</v>
+        <v>-23.14292698949723</v>
       </c>
       <c r="F21">
-        <v>-2.37345002689229</v>
+        <v>-2.737199407339998</v>
       </c>
       <c r="G21">
-        <v>-4.411243491927483</v>
+        <v>-3.918674042230402</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.481190208512494</v>
       </c>
       <c r="E22">
-        <v>-23.50023717412445</v>
+        <v>-23.35484145916017</v>
       </c>
       <c r="F22">
-        <v>-1.768210839343457</v>
+        <v>-2.532610054563979</v>
       </c>
       <c r="G22">
-        <v>-4.362826763415643</v>
+        <v>-4.304488329922606</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.776389456267246</v>
       </c>
       <c r="E23">
-        <v>-24.12610850977655</v>
+        <v>-23.57440452142207</v>
       </c>
       <c r="F23">
-        <v>-1.730665915178972</v>
+        <v>-2.397690542200412</v>
       </c>
       <c r="G23">
-        <v>-4.128989689794762</v>
+        <v>-4.323368371133069</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.09003814738619</v>
       </c>
       <c r="E24">
-        <v>-24.03865461974042</v>
+        <v>-24.01766514271487</v>
       </c>
       <c r="F24">
-        <v>-1.458864488074607</v>
+        <v>-2.099144445129262</v>
       </c>
       <c r="G24">
-        <v>-5.838492505909157</v>
+        <v>-4.54734995068354</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.39781939707314</v>
       </c>
       <c r="E25">
-        <v>-23.83358267430307</v>
+        <v>-24.01872933410667</v>
       </c>
       <c r="F25">
-        <v>-1.671406167917501</v>
+        <v>-1.935978432697635</v>
       </c>
       <c r="G25">
-        <v>-5.686766893298818</v>
+        <v>-5.447129743893135</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.67653757369183</v>
       </c>
       <c r="E26">
-        <v>-24.10968826302474</v>
+        <v>-24.6535308205019</v>
       </c>
       <c r="F26">
-        <v>-1.461651944385027</v>
+        <v>-1.792965770808717</v>
       </c>
       <c r="G26">
-        <v>-5.489259746425899</v>
+        <v>-5.382262914596655</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.90066251612179</v>
       </c>
       <c r="E27">
-        <v>-24.18890938731492</v>
+        <v>-23.82085766234152</v>
       </c>
       <c r="F27">
-        <v>-1.494387367408858</v>
+        <v>-1.515920778044631</v>
       </c>
       <c r="G27">
-        <v>-6.011994887076821</v>
+        <v>-5.931300339557085</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.05558734523673</v>
       </c>
       <c r="E28">
-        <v>-23.98677189303454</v>
+        <v>-24.04774779554782</v>
       </c>
       <c r="F28">
-        <v>-1.194230924106665</v>
+        <v>-1.553050690140313</v>
       </c>
       <c r="G28">
-        <v>-5.539285400069827</v>
+        <v>-5.960138501749676</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.12806417257806</v>
       </c>
       <c r="E29">
-        <v>-24.61100844956988</v>
+        <v>-23.80667448174949</v>
       </c>
       <c r="F29">
-        <v>-1.215670729225922</v>
+        <v>-1.648274836561728</v>
       </c>
       <c r="G29">
-        <v>-6.531101669816699</v>
+        <v>-5.886799986418201</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.1166136314452</v>
       </c>
       <c r="E30">
-        <v>-24.10727911485266</v>
+        <v>-23.29022013507072</v>
       </c>
       <c r="F30">
-        <v>-0.9916661012630883</v>
+        <v>-1.346371366407031</v>
       </c>
       <c r="G30">
-        <v>-6.492067027363153</v>
+        <v>-6.116853106487696</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.03210361474306</v>
       </c>
       <c r="E31">
-        <v>-23.03024497076437</v>
+        <v>-22.831064570011</v>
       </c>
       <c r="F31">
-        <v>-1.18665136237105</v>
+        <v>-1.557844452300314</v>
       </c>
       <c r="G31">
-        <v>-6.88404224030394</v>
+        <v>-5.982041071037495</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.88588660877777</v>
       </c>
       <c r="E32">
-        <v>-23.44121757238248</v>
+        <v>-22.90515040477649</v>
       </c>
       <c r="F32">
-        <v>-1.080617849710505</v>
+        <v>-1.443452712545522</v>
       </c>
       <c r="G32">
-        <v>-5.879102968039396</v>
+        <v>-6.224174371779789</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.6987759064772</v>
       </c>
       <c r="E33">
-        <v>-23.56708650742567</v>
+        <v>-22.74651343181378</v>
       </c>
       <c r="F33">
-        <v>-1.285319860453305</v>
+        <v>-1.521519713320153</v>
       </c>
       <c r="G33">
-        <v>-5.590694861749169</v>
+        <v>-5.121991134844693</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.49419797807729</v>
       </c>
       <c r="E34">
-        <v>-22.98181746972634</v>
+        <v>-22.50248755296245</v>
       </c>
       <c r="F34">
-        <v>-1.440571650718585</v>
+        <v>-1.158694790893969</v>
       </c>
       <c r="G34">
-        <v>-6.577151358267962</v>
+        <v>-5.438270724030045</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.29120849147759</v>
       </c>
       <c r="E35">
-        <v>-22.6073715394541</v>
+        <v>-21.91087412317837</v>
       </c>
       <c r="F35">
-        <v>-0.9968450542653908</v>
+        <v>-1.465350604838527</v>
       </c>
       <c r="G35">
-        <v>-6.331177824700112</v>
+        <v>-5.778720606197616</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.11104082241417</v>
       </c>
       <c r="E36">
-        <v>-21.309048984507</v>
+        <v>-22.11094210483725</v>
       </c>
       <c r="F36">
-        <v>-0.9499230111012156</v>
+        <v>-1.212018457346979</v>
       </c>
       <c r="G36">
-        <v>-5.078063506084104</v>
+        <v>-5.412243215000295</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.96132189820155</v>
       </c>
       <c r="E37">
-        <v>-21.65439041233194</v>
+        <v>-21.36990261822207</v>
       </c>
       <c r="F37">
-        <v>-1.271802561174422</v>
+        <v>-1.551144616746472</v>
       </c>
       <c r="G37">
-        <v>-5.56548174692208</v>
+        <v>-4.65473411634088</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.847115809663007</v>
       </c>
       <c r="E38">
-        <v>-19.711466753237</v>
+        <v>-20.74666685444243</v>
       </c>
       <c r="F38">
-        <v>-1.132265728907651</v>
+        <v>-1.09294064319455</v>
       </c>
       <c r="G38">
-        <v>-4.924172796691083</v>
+        <v>-4.64977822966859</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.769549394206212</v>
       </c>
       <c r="E39">
-        <v>-19.61031422932767</v>
+        <v>-20.2637141584724</v>
       </c>
       <c r="F39">
-        <v>-1.158650059054218</v>
+        <v>-1.526672158565566</v>
       </c>
       <c r="G39">
-        <v>-5.526834438296627</v>
+        <v>-4.484389995617681</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.718386615351093</v>
       </c>
       <c r="E40">
-        <v>-18.89149596466813</v>
+        <v>-20.70990017397416</v>
       </c>
       <c r="F40">
-        <v>-1.214442260367571</v>
+        <v>-1.678793548415667</v>
       </c>
       <c r="G40">
-        <v>-4.83628774426005</v>
+        <v>-4.476828709605985</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.687389411932759</v>
       </c>
       <c r="E41">
-        <v>-19.0170524350048</v>
+        <v>-19.49875527214871</v>
       </c>
       <c r="F41">
-        <v>-1.124494814301989</v>
+        <v>-1.401018763969714</v>
       </c>
       <c r="G41">
-        <v>-4.463109808891246</v>
+        <v>-4.392648157633397</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.668619712688294</v>
       </c>
       <c r="E42">
-        <v>-18.69391411523947</v>
+        <v>-18.9365225817264</v>
       </c>
       <c r="F42">
-        <v>-1.30508139321449</v>
+        <v>-1.920929482090977</v>
       </c>
       <c r="G42">
-        <v>-4.918332994359808</v>
+        <v>-3.33994102378271</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.653671091093537</v>
       </c>
       <c r="E43">
-        <v>-18.93768639954637</v>
+        <v>-18.75253068279475</v>
       </c>
       <c r="F43">
-        <v>-1.524446335354243</v>
+        <v>-1.830633293348816</v>
       </c>
       <c r="G43">
-        <v>-3.79980890464287</v>
+        <v>-3.4959703455941</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.641365403845505</v>
       </c>
       <c r="E44">
-        <v>-18.49075771430736</v>
+        <v>-18.22254978425507</v>
       </c>
       <c r="F44">
-        <v>-1.24479529874095</v>
+        <v>-1.713774675468487</v>
       </c>
       <c r="G44">
-        <v>-5.015216109566579</v>
+        <v>-3.865155763042544</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.625351563752361</v>
       </c>
       <c r="E45">
-        <v>-16.9767394139009</v>
+        <v>-17.01484199420144</v>
       </c>
       <c r="F45">
-        <v>-1.797422387435779</v>
+        <v>-2.012008478028782</v>
       </c>
       <c r="G45">
-        <v>-4.541940519272371</v>
+        <v>-3.076587126133687</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.605627214903219</v>
       </c>
       <c r="E46">
-        <v>-17.74798835062125</v>
+        <v>-17.04258342597243</v>
       </c>
       <c r="F46">
-        <v>-1.64143749201902</v>
+        <v>-2.03131523708583</v>
       </c>
       <c r="G46">
-        <v>-3.582451726716481</v>
+        <v>-2.386149680099906</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.586497849937471</v>
       </c>
       <c r="E47">
-        <v>-17.37736445241149</v>
+        <v>-16.60641892344965</v>
       </c>
       <c r="F47">
-        <v>-1.525142163972595</v>
+        <v>-2.092963995936975</v>
       </c>
       <c r="G47">
-        <v>-3.243488279496044</v>
+        <v>-3.211700421227962</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.56659985503185</v>
       </c>
       <c r="E48">
-        <v>-15.43818584132089</v>
+        <v>-16.03744333522992</v>
       </c>
       <c r="F48">
-        <v>-1.729604776535986</v>
+        <v>-2.260397757227825</v>
       </c>
       <c r="G48">
-        <v>-3.823171424513507</v>
+        <v>-2.965680540022563</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.549919476857438</v>
       </c>
       <c r="E49">
-        <v>-14.92765021017015</v>
+        <v>-15.13270404171147</v>
       </c>
       <c r="F49">
-        <v>-1.757138052270236</v>
+        <v>-2.190853828660598</v>
       </c>
       <c r="G49">
-        <v>-3.382448428506952</v>
+        <v>-2.927043163033729</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.538718957452049</v>
       </c>
       <c r="E50">
-        <v>-14.11976591872775</v>
+        <v>-15.26274822978974</v>
       </c>
       <c r="F50">
-        <v>-1.86207646322428</v>
+        <v>-2.362837812095026</v>
       </c>
       <c r="G50">
-        <v>-3.88461514972238</v>
+        <v>-2.299655056795368</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.532928105958158</v>
       </c>
       <c r="E51">
-        <v>-14.44966977866054</v>
+        <v>-15.13623625143745</v>
       </c>
       <c r="F51">
-        <v>-1.89747757255032</v>
+        <v>-2.319182021600089</v>
       </c>
       <c r="G51">
-        <v>-4.009270431458098</v>
+        <v>-2.974721639890312</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.536159576420404</v>
       </c>
       <c r="E52">
-        <v>-14.83998801032966</v>
+        <v>-13.74770649425755</v>
       </c>
       <c r="F52">
-        <v>-2.191598530955715</v>
+        <v>-2.344715618423981</v>
       </c>
       <c r="G52">
-        <v>-3.385083622756212</v>
+        <v>-2.907487770533254</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.543427840271187</v>
       </c>
       <c r="E53">
-        <v>-13.31853395560261</v>
+        <v>-13.1591226135846</v>
       </c>
       <c r="F53">
-        <v>-1.840618434022162</v>
+        <v>-2.481926395023691</v>
       </c>
       <c r="G53">
-        <v>-3.266850799366681</v>
+        <v>-2.676057463519423</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.552316713189178</v>
       </c>
       <c r="E54">
-        <v>-13.40518177726538</v>
+        <v>-12.47402789486018</v>
       </c>
       <c r="F54">
-        <v>-2.183972580645543</v>
+        <v>-2.701047797147022</v>
       </c>
       <c r="G54">
-        <v>-3.638641616154531</v>
+        <v>-2.910020337870797</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.562291852062561</v>
       </c>
       <c r="E55">
-        <v>-11.35851077865471</v>
+        <v>-11.89874867082177</v>
       </c>
       <c r="F55">
-        <v>-1.812631212951177</v>
+        <v>-2.263008771281449</v>
       </c>
       <c r="G55">
-        <v>-4.815868299373826</v>
+        <v>-2.766746548022218</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.566202378800648</v>
       </c>
       <c r="E56">
-        <v>-11.28622274807027</v>
+        <v>-12.538862057228</v>
       </c>
       <c r="F56">
-        <v>-2.300327551144969</v>
+        <v>-2.527521393608582</v>
       </c>
       <c r="G56">
-        <v>-5.203529871476943</v>
+        <v>-2.635682050122472</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.561776186946336</v>
       </c>
       <c r="E57">
-        <v>-11.42329965628245</v>
+        <v>-11.67735157658677</v>
       </c>
       <c r="F57">
-        <v>-2.16097461644162</v>
+        <v>-2.372538822749211</v>
       </c>
       <c r="G57">
-        <v>-5.245742637648189</v>
+        <v>-2.850331201797737</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.542447957136208</v>
       </c>
       <c r="E58">
-        <v>-10.83774985319465</v>
+        <v>-12.20172622430496</v>
       </c>
       <c r="F58">
-        <v>-1.483106660117534</v>
+        <v>-2.31580311096407</v>
       </c>
       <c r="G58">
-        <v>-5.123176310147753</v>
+        <v>-3.157430648202689</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.500034180622229</v>
       </c>
       <c r="E59">
-        <v>-10.49774296775074</v>
+        <v>-11.23151425358361</v>
       </c>
       <c r="F59">
-        <v>-1.791829250732076</v>
+        <v>-2.56455852855515</v>
       </c>
       <c r="G59">
-        <v>-4.891093825662685</v>
+        <v>-3.287813173721346</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.42830840650001</v>
       </c>
       <c r="E60">
-        <v>-9.42302740235438</v>
+        <v>-11.12580155634855</v>
       </c>
       <c r="F60">
-        <v>-2.076706457289632</v>
+        <v>-2.197818741783336</v>
       </c>
       <c r="G60">
-        <v>-4.675815670334958</v>
+        <v>-3.402242180286254</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.314314116461661</v>
       </c>
       <c r="E61">
-        <v>-10.17353139964559</v>
+        <v>-10.61943664975887</v>
       </c>
       <c r="F61">
-        <v>-2.40187379758455</v>
+        <v>-2.217234016970151</v>
       </c>
       <c r="G61">
-        <v>-4.371162717083528</v>
+        <v>-3.341374490001214</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.153172128022669</v>
       </c>
       <c r="E62">
-        <v>-9.386754325552941</v>
+        <v>-10.02210828577711</v>
       </c>
       <c r="F62">
-        <v>-2.088756717898157</v>
+        <v>-2.318538380128114</v>
       </c>
       <c r="G62">
-        <v>-5.1979118756968</v>
+        <v>-3.512738258750509</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.944743178665497</v>
       </c>
       <c r="E63">
-        <v>-10.70166468079015</v>
+        <v>-9.740672683148411</v>
       </c>
       <c r="F63">
-        <v>-2.118070983548425</v>
+        <v>-2.504742118398998</v>
       </c>
       <c r="G63">
-        <v>-5.433132757353096</v>
+        <v>-4.05091378379659</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.689311547168815</v>
       </c>
       <c r="E64">
-        <v>-9.460029563471055</v>
+        <v>-9.748171836105113</v>
       </c>
       <c r="F64">
-        <v>-2.308579747211658</v>
+        <v>-2.414003581463743</v>
       </c>
       <c r="G64">
-        <v>-5.088031558702849</v>
+        <v>-4.111877479902269</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.397666242311768</v>
       </c>
       <c r="E65">
-        <v>-9.579889213506075</v>
+        <v>-10.12643979843983</v>
       </c>
       <c r="F65">
-        <v>-2.435167540237868</v>
+        <v>-2.285099673179306</v>
       </c>
       <c r="G65">
-        <v>-4.791628484935282</v>
+        <v>-4.495728614089685</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.079082197414351</v>
       </c>
       <c r="E66">
-        <v>-8.370315692161292</v>
+        <v>-9.162350324576844</v>
       </c>
       <c r="F66">
-        <v>-2.503285848504877</v>
+        <v>-2.385201246868404</v>
       </c>
       <c r="G66">
-        <v>-4.74798887363661</v>
+        <v>-4.179048448894081</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.746065342623411</v>
       </c>
       <c r="E67">
-        <v>-8.264023350253252</v>
+        <v>-9.1793864437937</v>
       </c>
       <c r="F67">
-        <v>-1.878808656393427</v>
+        <v>-2.552966355120374</v>
       </c>
       <c r="G67">
-        <v>-5.466261386564582</v>
+        <v>-4.063149560109736</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.413006541359927</v>
       </c>
       <c r="E68">
-        <v>-8.199071447561236</v>
+        <v>-9.654862629177066</v>
       </c>
       <c r="F68">
-        <v>-2.274826260649787</v>
+        <v>-2.466950340748479</v>
       </c>
       <c r="G68">
-        <v>-4.626078034152949</v>
+        <v>-4.007817101966357</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.08742576248281</v>
       </c>
       <c r="E69">
-        <v>-7.910471799052405</v>
+        <v>-8.658960625410201</v>
       </c>
       <c r="F69">
-        <v>-1.990161116147348</v>
+        <v>-2.393992710114315</v>
       </c>
       <c r="G69">
-        <v>-5.807379998931085</v>
+        <v>-4.13440243175147</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.781155600615136</v>
       </c>
       <c r="E70">
-        <v>-8.53583594561565</v>
+        <v>-8.917214969593633</v>
       </c>
       <c r="F70">
-        <v>-1.869274147587205</v>
+        <v>-2.612789392215749</v>
       </c>
       <c r="G70">
-        <v>-6.066575851382784</v>
+        <v>-4.752050913013296</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.502238399221471</v>
       </c>
       <c r="E71">
-        <v>-8.500930467964528</v>
+        <v>-9.296569765690187</v>
       </c>
       <c r="F71">
-        <v>-2.847002820050684</v>
+        <v>-2.692368163500489</v>
       </c>
       <c r="G71">
-        <v>-4.956940576438789</v>
+        <v>-4.463622943449833</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.252630425585103</v>
       </c>
       <c r="E72">
-        <v>-8.232410073205706</v>
+        <v>-8.610832003656679</v>
       </c>
       <c r="F72">
-        <v>-2.439779061569253</v>
+        <v>-2.816421152274132</v>
       </c>
       <c r="G72">
-        <v>-5.296768076044977</v>
+        <v>-3.838042395075913</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.035484694198156</v>
       </c>
       <c r="E73">
-        <v>-8.763853668849869</v>
+        <v>-9.282522439318393</v>
       </c>
       <c r="F73">
-        <v>-2.857547937088321</v>
+        <v>-2.767887106144109</v>
       </c>
       <c r="G73">
-        <v>-5.717627798815904</v>
+        <v>-4.363783511076492</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.843536526579733</v>
       </c>
       <c r="E74">
-        <v>-9.266677308765555</v>
+        <v>-9.522169283804308</v>
       </c>
       <c r="F74">
-        <v>-2.56897621191428</v>
+        <v>-3.074209088025338</v>
       </c>
       <c r="G74">
-        <v>-5.522563834550968</v>
+        <v>-4.131442804039361</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.669515921526377</v>
       </c>
       <c r="E75">
-        <v>-9.444492369150739</v>
+        <v>-9.259920825546111</v>
       </c>
       <c r="F75">
-        <v>-2.986745087433349</v>
+        <v>-3.166045211769302</v>
       </c>
       <c r="G75">
-        <v>-4.559804223002279</v>
+        <v>-3.541189087115005</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.505032686569179</v>
       </c>
       <c r="E76">
-        <v>-8.623181152275595</v>
+        <v>-10.4158319299</v>
       </c>
       <c r="F76">
-        <v>-3.000186176911174</v>
+        <v>-3.033221468934818</v>
       </c>
       <c r="G76">
-        <v>-4.290246363012661</v>
+        <v>-3.732296949460513</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.337729700294517</v>
       </c>
       <c r="E77">
-        <v>-8.904182021399558</v>
+        <v>-9.714932836888812</v>
       </c>
       <c r="F77">
-        <v>-3.109254827735576</v>
+        <v>-3.279710473311839</v>
       </c>
       <c r="G77">
-        <v>-4.585497366932562</v>
+        <v>-4.252234679130749</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.163682260463204</v>
       </c>
       <c r="E78">
-        <v>-11.06699479288494</v>
+        <v>-9.896773710666816</v>
       </c>
       <c r="F78">
-        <v>-3.164208721237296</v>
+        <v>-3.40668345718035</v>
       </c>
       <c r="G78">
-        <v>-3.957927180689541</v>
+        <v>-3.388900681762991</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.980630534848906</v>
       </c>
       <c r="E79">
-        <v>-11.59517788724358</v>
+        <v>-11.12231463136264</v>
       </c>
       <c r="F79">
-        <v>-3.608629489574036</v>
+        <v>-3.438423182586016</v>
       </c>
       <c r="G79">
-        <v>-4.407638307835217</v>
+        <v>-3.425157776509089</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.787044191123571</v>
       </c>
       <c r="E80">
-        <v>-10.69535198802345</v>
+        <v>-11.49503521303796</v>
       </c>
       <c r="F80">
-        <v>-4.077582358544684</v>
+        <v>-3.63231417035488</v>
       </c>
       <c r="G80">
-        <v>-4.065605984899875</v>
+        <v>-3.302382884639678</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.586176519320448</v>
       </c>
       <c r="E81">
-        <v>-12.40068020135795</v>
+        <v>-12.06892872403002</v>
       </c>
       <c r="F81">
-        <v>-3.551670118590139</v>
+        <v>-3.749374909881491</v>
       </c>
       <c r="G81">
-        <v>-3.262848349809702</v>
+        <v>-3.079788423670162</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.3785075083085</v>
       </c>
       <c r="E82">
-        <v>-12.11500141858406</v>
+        <v>-13.46823624934818</v>
       </c>
       <c r="F82">
-        <v>-3.991814026026226</v>
+        <v>-3.924008012270072</v>
       </c>
       <c r="G82">
-        <v>-3.604102694543315</v>
+        <v>-3.389340984319714</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.169289990909416</v>
       </c>
       <c r="E83">
-        <v>-13.44928458562608</v>
+        <v>-14.05627671314021</v>
       </c>
       <c r="F83">
-        <v>-4.116338355852061</v>
+        <v>-4.220164269384146</v>
       </c>
       <c r="G83">
-        <v>-4.146045620413087</v>
+        <v>-2.884181529936785</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.965978155018293</v>
       </c>
       <c r="E84">
-        <v>-13.65218286353975</v>
+        <v>-14.76299036677724</v>
       </c>
       <c r="F84">
-        <v>-4.146518265438256</v>
+        <v>-4.251712641919765</v>
       </c>
       <c r="G84">
-        <v>-3.107530795289255</v>
+        <v>-3.060497874812829</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.774422155230443</v>
       </c>
       <c r="E85">
-        <v>-15.83523791383942</v>
+        <v>-15.98397111414735</v>
       </c>
       <c r="F85">
-        <v>-4.316095013200148</v>
+        <v>-4.33970514091474</v>
       </c>
       <c r="G85">
-        <v>-3.266860731003298</v>
+        <v>-3.024892957537967</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.604743335535551</v>
       </c>
       <c r="E86">
-        <v>-17.4747855137385</v>
+        <v>-16.6085699486033</v>
       </c>
       <c r="F86">
-        <v>-4.485793530970252</v>
+        <v>-4.585995337115088</v>
       </c>
       <c r="G86">
-        <v>-3.603682255259828</v>
+        <v>-2.341907549513086</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.470943856648876</v>
       </c>
       <c r="E87">
-        <v>-18.30975913669478</v>
+        <v>-17.91017564720596</v>
       </c>
       <c r="F87">
-        <v>-4.917160057406275</v>
+        <v>-4.717397601486368</v>
       </c>
       <c r="G87">
-        <v>-2.661924744612274</v>
+        <v>-2.701293752165287</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.384901132177839</v>
       </c>
       <c r="E88">
-        <v>-18.83368999396022</v>
+        <v>-19.39662006937971</v>
       </c>
       <c r="F88">
-        <v>-5.342573935685781</v>
+        <v>-5.027718112820911</v>
       </c>
       <c r="G88">
-        <v>-3.619672190214507</v>
+        <v>-2.518104714749716</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.361206976702376</v>
       </c>
       <c r="E89">
-        <v>-19.3033335048217</v>
+        <v>-20.68624795423209</v>
       </c>
       <c r="F89">
-        <v>-5.042651920358581</v>
+        <v>-5.037347883878455</v>
       </c>
       <c r="G89">
-        <v>-2.737001296351866</v>
+        <v>-2.594975582171593</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.412024338344082</v>
       </c>
       <c r="E90">
-        <v>-22.4512705119357</v>
+        <v>-22.69343971644389</v>
       </c>
       <c r="F90">
-        <v>-5.085799093268198</v>
+        <v>-5.379354276737482</v>
       </c>
       <c r="G90">
-        <v>-4.243435249087367</v>
+        <v>-2.797743185906414</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.546251340156541</v>
       </c>
       <c r="E91">
-        <v>-24.40215975681013</v>
+        <v>-24.11188910139247</v>
       </c>
       <c r="F91">
-        <v>-5.249177996122345</v>
+        <v>-5.406458458157082</v>
       </c>
       <c r="G91">
-        <v>-3.286502197687794</v>
+        <v>-2.617639576933444</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.773443543422331</v>
       </c>
       <c r="E92">
-        <v>-26.08345988705992</v>
+        <v>-26.21205043498173</v>
       </c>
       <c r="F92">
-        <v>-5.684819726724216</v>
+        <v>-5.667553236580264</v>
       </c>
       <c r="G92">
-        <v>-3.952560786370382</v>
+        <v>-2.670998949935417</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.095137056873974</v>
       </c>
       <c r="E93">
-        <v>-27.71813937740076</v>
+        <v>-27.02091287680979</v>
       </c>
       <c r="F93">
-        <v>-5.750035435611816</v>
+        <v>-5.679851179042225</v>
       </c>
       <c r="G93">
-        <v>-4.908662890839597</v>
+        <v>-3.207539065485098</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.505795686647938</v>
       </c>
       <c r="E94">
-        <v>-30.04130541349775</v>
+        <v>-30.2381106296341</v>
       </c>
       <c r="F94">
-        <v>-5.341476348877071</v>
+        <v>-6.233032445529526</v>
       </c>
       <c r="G94">
-        <v>-5.346730829323657</v>
+        <v>-3.799256043537812</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.998284921438909</v>
       </c>
       <c r="E95">
-        <v>-31.72559433659261</v>
+        <v>-32.83042878261399</v>
       </c>
       <c r="F95">
-        <v>-5.805412624856365</v>
+        <v>-6.452415611752142</v>
       </c>
       <c r="G95">
-        <v>-5.460722843877382</v>
+        <v>-4.01570944253198</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.556927166106028</v>
       </c>
       <c r="E96">
-        <v>-33.95062607670638</v>
+        <v>-34.60996962798618</v>
       </c>
       <c r="F96">
-        <v>-6.216208303578668</v>
+        <v>-6.373751772263794</v>
       </c>
       <c r="G96">
-        <v>-4.477255769980551</v>
+        <v>-4.743976492443013</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.154591992912449</v>
       </c>
       <c r="E97">
-        <v>-36.76043325085265</v>
+        <v>-37.10859818222137</v>
       </c>
       <c r="F97">
-        <v>-6.403869140111077</v>
+        <v>-6.694153100706704</v>
       </c>
       <c r="G97">
-        <v>-5.993154572412828</v>
+        <v>-5.202831346368156</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.777484083290579</v>
       </c>
       <c r="E98">
-        <v>-39.44863278399693</v>
+        <v>-39.73805208630116</v>
       </c>
       <c r="F98">
-        <v>-6.192624683620966</v>
+        <v>-6.789308492633687</v>
       </c>
       <c r="G98">
-        <v>-6.72692374901013</v>
+        <v>-5.260514291844418</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.380951958189829</v>
       </c>
       <c r="E99">
-        <v>-40.85551418209293</v>
+        <v>-42.37181483339924</v>
       </c>
       <c r="F99">
-        <v>-6.734222888714922</v>
+        <v>-6.951784475018782</v>
       </c>
       <c r="G99">
-        <v>-7.339954019244671</v>
+        <v>-6.16729919941511</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.972386020260356</v>
       </c>
       <c r="E100">
-        <v>-44.02190698502518</v>
+        <v>-44.98209744276755</v>
       </c>
       <c r="F100">
-        <v>-6.883577117255972</v>
+        <v>-6.96352534040236</v>
       </c>
       <c r="G100">
-        <v>-7.730326928144451</v>
+        <v>-6.30434254255878</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.488834911032004</v>
       </c>
       <c r="E101">
-        <v>-46.29837086868107</v>
+        <v>-47.37102824264094</v>
       </c>
       <c r="F101">
-        <v>-7.067212916578177</v>
+        <v>-7.090582817745957</v>
       </c>
       <c r="G101">
-        <v>-8.541162294350446</v>
+        <v>-6.714413197417223</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.98644851753207</v>
       </c>
       <c r="E102">
-        <v>-50.04838208053686</v>
+        <v>-48.88992031319815</v>
       </c>
       <c r="F102">
-        <v>-6.903668340243471</v>
+        <v>-7.043472320997645</v>
       </c>
       <c r="G102">
-        <v>-9.334825860844242</v>
+        <v>-7.926178802247735</v>
       </c>
     </row>
   </sheetData>
